--- a/marketing_forms/026_promotional_strategy_evaluation_form--marketing_forms.xlsx
+++ b/marketing_forms/026_promotional_strategy_evaluation_form--marketing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>channel_a</t>
+          <t>channel a</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>channel_b</t>
+          <t>channel b</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>channel_c</t>
+          <t>channel c</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>channel_a</t>
+          <t>channel a</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>channel_b</t>
+          <t>channel b</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>channel_c</t>
+          <t>channel c</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>channel_a</t>
+          <t>channel a</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>channel_b</t>
+          <t>channel b</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>channel_c</t>
+          <t>channel c</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>channel_a</t>
+          <t>channel a</t>
         </is>
       </c>
     </row>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>channel_b</t>
+          <t>channel b</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>channel_c</t>
+          <t>channel c</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>channel_a</t>
+          <t>channel a</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>channel_b</t>
+          <t>channel b</t>
         </is>
       </c>
     </row>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>channel_c</t>
+          <t>channel c</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>channel_a</t>
+          <t>channel a</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>channel_b</t>
+          <t>channel b</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>channel_c</t>
+          <t>channel c</t>
         </is>
       </c>
     </row>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>channel_a</t>
+          <t>channel a</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>channel_b</t>
+          <t>channel b</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>channel_c</t>
+          <t>channel c</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>channel_a</t>
+          <t>channel a</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>channel_b</t>
+          <t>channel b</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>channel_c</t>
+          <t>channel c</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>channel_a</t>
+          <t>channel a</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>channel_b</t>
+          <t>channel b</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>channel_c</t>
+          <t>channel c</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>channel_a</t>
+          <t>channel a</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>channel_b</t>
+          <t>channel b</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>channel_c</t>
+          <t>channel c</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>channel_a</t>
+          <t>channel a</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>channel_b</t>
+          <t>channel b</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>channel_c</t>
+          <t>channel c</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>channel_a</t>
+          <t>channel a</t>
         </is>
       </c>
     </row>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>channel_b</t>
+          <t>channel b</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>channel_c</t>
+          <t>channel c</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>channel_a</t>
+          <t>channel a</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>channel_b</t>
+          <t>channel b</t>
         </is>
       </c>
     </row>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>channel_c</t>
+          <t>channel c</t>
         </is>
       </c>
     </row>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>channel_a</t>
+          <t>channel a</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>channel_b</t>
+          <t>channel b</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>channel_c</t>
+          <t>channel c</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>channel_a</t>
+          <t>channel a</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>channel_b</t>
+          <t>channel b</t>
         </is>
       </c>
     </row>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>channel_c</t>
+          <t>channel c</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>channel_a</t>
+          <t>channel a</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>channel_b</t>
+          <t>channel b</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>channel_c</t>
+          <t>channel c</t>
         </is>
       </c>
     </row>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>channel_a</t>
+          <t>channel a</t>
         </is>
       </c>
     </row>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>channel_b</t>
+          <t>channel b</t>
         </is>
       </c>
     </row>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>channel_c</t>
+          <t>channel c</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>channel_a</t>
+          <t>channel a</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>channel_b</t>
+          <t>channel b</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>channel_c</t>
+          <t>channel c</t>
         </is>
       </c>
     </row>
